--- a/data/fmsForecastOutput/File1/RPT_RPT4431929423193CE_fmsForecastOutput.xlsx
+++ b/data/fmsForecastOutput/File1/RPT_RPT4431929423193CE_fmsForecastOutput.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="FMS Forecast Output" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FMS Forecast Output" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1878,13 +1878,13 @@
         <v>173.8198424841217</v>
       </c>
       <c r="D8" s="149" t="n">
-        <v>209.4488727090951</v>
+        <v>209.448872709095</v>
       </c>
       <c r="E8" s="149" t="n">
-        <v>280.9281489347429</v>
+        <v>280.9281489347428</v>
       </c>
       <c r="F8" s="149" t="n">
-        <v>276.6502868378217</v>
+        <v>276.6502868378216</v>
       </c>
       <c r="G8" s="150" t="n">
         <v>296.4313519362281</v>
@@ -1896,25 +1896,25 @@
         <v>153.6763140653386</v>
       </c>
       <c r="J8" s="149" t="n">
-        <v>150.2906984341076</v>
+        <v>150.2906984341075</v>
       </c>
       <c r="K8" s="149" t="n">
-        <v>131.8944711841467</v>
+        <v>131.8944711841466</v>
       </c>
       <c r="L8" s="150" t="n">
         <v>126.926431937151</v>
       </c>
       <c r="M8" s="151" t="n">
-        <v>28513.36897377078</v>
+        <v>28513.36897377076</v>
       </c>
       <c r="N8" s="152" t="n">
         <v>27589.43109853494</v>
       </c>
       <c r="O8" s="152" t="n">
-        <v>27615.53982529069</v>
+        <v>27615.53982529068</v>
       </c>
       <c r="P8" s="152" t="n">
-        <v>24878.69309532181</v>
+        <v>24878.69309532179</v>
       </c>
       <c r="Q8" s="153" t="n">
         <v>24703.52033841372</v>
@@ -1925,16 +1925,16 @@
         </is>
       </c>
       <c r="T8" s="148" t="n">
-        <v>166.0699132013902</v>
+        <v>166.0699132013901</v>
       </c>
       <c r="U8" s="149" t="n">
         <v>200.1103879386258</v>
       </c>
       <c r="V8" s="149" t="n">
-        <v>268.402690065041</v>
+        <v>268.4026900650409</v>
       </c>
       <c r="W8" s="149" t="n">
-        <v>264.3155606730782</v>
+        <v>264.3155606730779</v>
       </c>
       <c r="X8" s="150" t="n">
         <v>283.2146674549949</v>
@@ -1955,16 +1955,16 @@
         <v>124.4398981496567</v>
       </c>
       <c r="AD8" s="151" t="n">
-        <v>28513.36897377078</v>
+        <v>28513.36897377076</v>
       </c>
       <c r="AE8" s="152" t="n">
         <v>27589.43109853494</v>
       </c>
       <c r="AF8" s="152" t="n">
-        <v>27615.53982529069</v>
+        <v>27615.53982529068</v>
       </c>
       <c r="AG8" s="152" t="n">
-        <v>24878.69309532181</v>
+        <v>24878.69309532179</v>
       </c>
       <c r="AH8" s="153" t="n">
         <v>24703.52033841372</v>
@@ -2031,22 +2031,22 @@
         <v>552.6331428004989</v>
       </c>
       <c r="F9" s="156" t="n">
-        <v>601.9135476813774</v>
+        <v>601.9135476813773</v>
       </c>
       <c r="G9" s="157" t="n">
-        <v>629.8372385861558</v>
+        <v>629.8372385861555</v>
       </c>
       <c r="H9" s="155" t="n">
         <v>282.6116213425473</v>
       </c>
       <c r="I9" s="156" t="n">
-        <v>282.2815238382445</v>
+        <v>282.2815238382444</v>
       </c>
       <c r="J9" s="156" t="n">
         <v>294.1036792367452</v>
       </c>
       <c r="K9" s="156" t="n">
-        <v>304.9610529054244</v>
+        <v>304.9610529054243</v>
       </c>
       <c r="L9" s="157" t="n">
         <v>315.1345367056911</v>
@@ -2055,16 +2055,16 @@
         <v>26067.5011594592</v>
       </c>
       <c r="N9" s="159" t="n">
-        <v>26846.67687501294</v>
+        <v>26846.67687501293</v>
       </c>
       <c r="O9" s="159" t="n">
         <v>28955.51136409166</v>
       </c>
       <c r="P9" s="159" t="n">
-        <v>31138.89096503099</v>
+        <v>31138.89096503098</v>
       </c>
       <c r="Q9" s="160" t="n">
-        <v>33503.64851975265</v>
+        <v>33503.64851975264</v>
       </c>
       <c r="S9" s="32" t="inlineStr">
         <is>
@@ -2072,22 +2072,22 @@
         </is>
       </c>
       <c r="T9" s="155" t="n">
-        <v>326.4669752499567</v>
+        <v>326.4669752499568</v>
       </c>
       <c r="U9" s="156" t="n">
-        <v>415.4503588273536</v>
+        <v>415.4503588273535</v>
       </c>
       <c r="V9" s="156" t="n">
         <v>555.1266193412753</v>
       </c>
       <c r="W9" s="156" t="n">
-        <v>604.6293770344874</v>
+        <v>604.6293770344873</v>
       </c>
       <c r="X9" s="157" t="n">
-        <v>632.6790594204319</v>
+        <v>632.6790594204318</v>
       </c>
       <c r="Y9" s="155" t="n">
-        <v>283.71979739717</v>
+        <v>283.7197973971701</v>
       </c>
       <c r="Z9" s="156" t="n">
         <v>283.1495795426982</v>
@@ -2096,7 +2096,7 @@
         <v>294.8083992687835</v>
       </c>
       <c r="AB9" s="156" t="n">
-        <v>305.6566493308542</v>
+        <v>305.6566493308541</v>
       </c>
       <c r="AC9" s="157" t="n">
         <v>315.8443661912866</v>
@@ -2105,16 +2105,16 @@
         <v>26067.5011594592</v>
       </c>
       <c r="AE9" s="159" t="n">
-        <v>26846.67687501294</v>
+        <v>26846.67687501293</v>
       </c>
       <c r="AF9" s="159" t="n">
         <v>28955.51136409166</v>
       </c>
       <c r="AG9" s="159" t="n">
-        <v>31138.89096503099</v>
+        <v>31138.89096503098</v>
       </c>
       <c r="AH9" s="160" t="n">
-        <v>33503.64851975265</v>
+        <v>33503.64851975264</v>
       </c>
       <c r="AJ9" s="39" t="n"/>
       <c r="AQ9" s="40" t="inlineStr">
@@ -2170,16 +2170,16 @@
         </is>
       </c>
       <c r="C10" s="161" t="n">
-        <v>223.4655704434068</v>
+        <v>223.4655704434067</v>
       </c>
       <c r="D10" s="162" t="n">
         <v>276.8366966654077</v>
       </c>
       <c r="E10" s="162" t="n">
-        <v>375.396955849918</v>
+        <v>375.3969558499179</v>
       </c>
       <c r="F10" s="162" t="n">
-        <v>395.4327373234509</v>
+        <v>395.4327373234506</v>
       </c>
       <c r="G10" s="163" t="n">
         <v>426.3307829181931</v>
@@ -2194,7 +2194,7 @@
         <v>200.4637430759367</v>
       </c>
       <c r="K10" s="162" t="n">
-        <v>192.6767372344017</v>
+        <v>192.6767372344016</v>
       </c>
       <c r="L10" s="163" t="n">
         <v>193.4152612515544</v>
@@ -2206,10 +2206,10 @@
         <v>54436.10797354788</v>
       </c>
       <c r="O10" s="165" t="n">
-        <v>56571.05118938236</v>
+        <v>56571.05118938234</v>
       </c>
       <c r="P10" s="165" t="n">
-        <v>56017.5840603528</v>
+        <v>56017.58406035277</v>
       </c>
       <c r="Q10" s="166" t="n">
         <v>58207.16885816635</v>
@@ -2226,10 +2226,10 @@
         <v>268.8312782850271</v>
       </c>
       <c r="V10" s="162" t="n">
-        <v>364.8599954259165</v>
+        <v>364.8599954259164</v>
       </c>
       <c r="W10" s="162" t="n">
-        <v>384.6681071195779</v>
+        <v>384.6681071195778</v>
       </c>
       <c r="X10" s="163" t="n">
         <v>415.2297537793094</v>
@@ -2241,10 +2241,10 @@
         <v>194.0742920633844</v>
       </c>
       <c r="AA10" s="162" t="n">
-        <v>197.4191899626581</v>
+        <v>197.419189962658</v>
       </c>
       <c r="AB10" s="162" t="n">
-        <v>190.0848441192867</v>
+        <v>190.0848441192866</v>
       </c>
       <c r="AC10" s="163" t="n">
         <v>191.0974729433113</v>
@@ -2256,10 +2256,10 @@
         <v>54436.10797354788</v>
       </c>
       <c r="AF10" s="165" t="n">
-        <v>56571.05118938236</v>
+        <v>56571.05118938234</v>
       </c>
       <c r="AG10" s="165" t="n">
-        <v>56017.5840603528</v>
+        <v>56017.58406035277</v>
       </c>
       <c r="AH10" s="166" t="n">
         <v>58207.16885816635</v>
@@ -2318,7 +2318,7 @@
         </is>
       </c>
       <c r="C11" s="155" t="n">
-        <v>613.6687225753553</v>
+        <v>613.6687225753556</v>
       </c>
       <c r="D11" s="156" t="n">
         <v>746.0448097937978</v>
@@ -2333,7 +2333,7 @@
         <v>1172.055926114081</v>
       </c>
       <c r="H11" s="155" t="n">
-        <v>598.3102040399436</v>
+        <v>598.3102040399439</v>
       </c>
       <c r="I11" s="156" t="n">
         <v>662.052427863719</v>
@@ -2348,7 +2348,7 @@
         <v>759.903311773159</v>
       </c>
       <c r="M11" s="158" t="n">
-        <v>60243.92667147247</v>
+        <v>60243.92667147249</v>
       </c>
       <c r="N11" s="159" t="n">
         <v>70489.59896386128</v>
@@ -2368,7 +2368,7 @@
         </is>
       </c>
       <c r="T11" s="155" t="n">
-        <v>735.2791239843392</v>
+        <v>735.2791239843395</v>
       </c>
       <c r="U11" s="156" t="n">
         <v>893.8881093632524</v>
@@ -2383,7 +2383,7 @@
         <v>1404.321619973049</v>
       </c>
       <c r="Y11" s="155" t="n">
-        <v>713.3390953485633</v>
+        <v>713.3390953485635</v>
       </c>
       <c r="Z11" s="156" t="n">
         <v>775.9393119356628</v>
@@ -2398,7 +2398,7 @@
         <v>851.177651681036</v>
       </c>
       <c r="AD11" s="158" t="n">
-        <v>60243.92667147247</v>
+        <v>60243.92667147249</v>
       </c>
       <c r="AE11" s="159" t="n">
         <v>70489.59896386128</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="C12" s="161" t="n">
-        <v>335.3357078661715</v>
+        <v>335.3357078661716</v>
       </c>
       <c r="D12" s="162" t="n">
         <v>429.1201580598057</v>
@@ -2470,22 +2470,22 @@
         <v>584.2970108514849</v>
       </c>
       <c r="F12" s="162" t="n">
-        <v>657.8908687818222</v>
+        <v>657.8908687818221</v>
       </c>
       <c r="G12" s="163" t="n">
         <v>707.4349193391673</v>
       </c>
       <c r="H12" s="161" t="n">
-        <v>311.8071214912408</v>
+        <v>311.8071214912409</v>
       </c>
       <c r="I12" s="162" t="n">
-        <v>327.7970597571726</v>
+        <v>327.7970597571727</v>
       </c>
       <c r="J12" s="162" t="n">
         <v>351.8667508660705</v>
       </c>
       <c r="K12" s="162" t="n">
-        <v>360.9112440096552</v>
+        <v>360.911244009655</v>
       </c>
       <c r="L12" s="163" t="n">
         <v>361.9077836579761</v>
@@ -2500,7 +2500,7 @@
         <v>138857.4888072425</v>
       </c>
       <c r="P12" s="165" t="n">
-        <v>147985.1288310107</v>
+        <v>147985.1288310106</v>
       </c>
       <c r="Q12" s="166" t="n">
         <v>155023.030336775</v>
@@ -2511,7 +2511,7 @@
         </is>
       </c>
       <c r="T12" s="161" t="n">
-        <v>344.3273634553057</v>
+        <v>344.3273634553058</v>
       </c>
       <c r="U12" s="162" t="n">
         <v>444.0239698499896</v>
@@ -2520,7 +2520,7 @@
         <v>610.0421019959761</v>
       </c>
       <c r="W12" s="162" t="n">
-        <v>687.8886396201171</v>
+        <v>687.8886396201168</v>
       </c>
       <c r="X12" s="163" t="n">
         <v>741.3042481458612</v>
@@ -2535,7 +2535,7 @@
         <v>361.0424130117514</v>
       </c>
       <c r="AB12" s="162" t="n">
-        <v>369.7569759834527</v>
+        <v>369.7569759834525</v>
       </c>
       <c r="AC12" s="163" t="n">
         <v>370.5692395546512</v>
@@ -2550,7 +2550,7 @@
         <v>138857.4888072425</v>
       </c>
       <c r="AG12" s="165" t="n">
-        <v>147985.1288310107</v>
+        <v>147985.1288310106</v>
       </c>
       <c r="AH12" s="166" t="n">
         <v>155023.030336775</v>
@@ -2746,22 +2746,22 @@
         </is>
       </c>
       <c r="C14" s="167" t="n">
-        <v>332.2984115506637</v>
+        <v>332.2984115506638</v>
       </c>
       <c r="D14" s="168" t="n">
-        <v>424.4712217057528</v>
+        <v>424.4712217057527</v>
       </c>
       <c r="E14" s="168" t="n">
-        <v>576.3589261890756</v>
+        <v>576.3589261890755</v>
       </c>
       <c r="F14" s="168" t="n">
-        <v>648.2700529308527</v>
+        <v>648.2700529308526</v>
       </c>
       <c r="G14" s="169" t="n">
         <v>696.6115376608154</v>
       </c>
       <c r="H14" s="167" t="n">
-        <v>309.1794219356563</v>
+        <v>309.1794219356564</v>
       </c>
       <c r="I14" s="168" t="n">
         <v>325.0773770877086</v>
@@ -2770,13 +2770,13 @@
         <v>348.9723525930174</v>
       </c>
       <c r="K14" s="168" t="n">
-        <v>357.9966274266687</v>
+        <v>357.9966274266686</v>
       </c>
       <c r="L14" s="169" t="n">
         <v>359.0538535480448</v>
       </c>
       <c r="M14" s="170" t="n">
-        <v>114824.7968047024</v>
+        <v>114824.7968047025</v>
       </c>
       <c r="N14" s="171" t="n">
         <v>124925.7069374092</v>
@@ -2796,22 +2796,22 @@
         </is>
       </c>
       <c r="T14" s="167" t="n">
-        <v>335.5104868164794</v>
+        <v>335.5104868164795</v>
       </c>
       <c r="U14" s="168" t="n">
-        <v>430.3677469634199</v>
+        <v>430.3677469634198</v>
       </c>
       <c r="V14" s="168" t="n">
         <v>586.4306058728157</v>
       </c>
       <c r="W14" s="168" t="n">
-        <v>659.2451962066948</v>
+        <v>659.2451962066946</v>
       </c>
       <c r="X14" s="169" t="n">
         <v>708.9838515505846</v>
       </c>
       <c r="Y14" s="167" t="n">
-        <v>311.9582288805413</v>
+        <v>311.9582288805414</v>
       </c>
       <c r="Z14" s="168" t="n">
         <v>328.5245476171249</v>
@@ -2820,13 +2820,13 @@
         <v>352.6393793873116</v>
       </c>
       <c r="AB14" s="168" t="n">
-        <v>361.3184492802507</v>
+        <v>361.3184492802506</v>
       </c>
       <c r="AC14" s="169" t="n">
         <v>362.3127240369342</v>
       </c>
       <c r="AD14" s="170" t="n">
-        <v>114824.7968047024</v>
+        <v>114824.7968047025</v>
       </c>
       <c r="AE14" s="171" t="n">
         <v>124925.7069374092</v>
@@ -3736,7 +3736,7 @@
         <v>368.2558507821897</v>
       </c>
       <c r="N23" s="86" t="n">
-        <v>381.1068562663507</v>
+        <v>381.1068562663506</v>
       </c>
       <c r="O23" s="86" t="n">
         <v>394.6308892939284</v>
@@ -3942,7 +3942,7 @@
         </is>
       </c>
       <c r="C25" s="91" t="n">
-        <v>345.5472334907498</v>
+        <v>345.5472334907497</v>
       </c>
       <c r="D25" s="92" t="n">
         <v>294.3090144848707</v>
@@ -3975,7 +3975,7 @@
         <v>371.3856377821897</v>
       </c>
       <c r="N25" s="92" t="n">
-        <v>384.2952962663507</v>
+        <v>384.2952962663506</v>
       </c>
       <c r="O25" s="92" t="n">
         <v>397.9039822939284</v>
@@ -4408,46 +4408,46 @@
         </is>
       </c>
       <c r="C35" s="148" t="n">
-        <v>176.9719128457909</v>
+        <v>176.9719128457908</v>
       </c>
       <c r="D35" s="149" t="n">
         <v>218.7877020820015</v>
       </c>
       <c r="E35" s="149" t="n">
-        <v>295.7389391429957</v>
+        <v>295.7389391429955</v>
       </c>
       <c r="F35" s="149" t="n">
-        <v>295.0796240129791</v>
+        <v>295.079624012979</v>
       </c>
       <c r="G35" s="150" t="n">
         <v>316.9561178112163</v>
       </c>
       <c r="H35" s="148" t="n">
-        <v>165.5780096609861</v>
+        <v>165.578009660986</v>
       </c>
       <c r="I35" s="149" t="n">
         <v>160.5283770874522</v>
       </c>
       <c r="J35" s="149" t="n">
-        <v>158.2141621852478</v>
+        <v>158.2141621852477</v>
       </c>
       <c r="K35" s="149" t="n">
-        <v>140.6807540713814</v>
+        <v>140.6807540713813</v>
       </c>
       <c r="L35" s="150" t="n">
         <v>135.7147577395382</v>
       </c>
       <c r="M35" s="151" t="n">
-        <v>29030.43390703218</v>
+        <v>29030.43390703217</v>
       </c>
       <c r="N35" s="152" t="n">
         <v>28819.57851442785</v>
       </c>
       <c r="O35" s="152" t="n">
-        <v>29071.45646586571</v>
+        <v>29071.4564658657</v>
       </c>
       <c r="P35" s="152" t="n">
-        <v>26536.01226448546</v>
+        <v>26536.01226448544</v>
       </c>
       <c r="Q35" s="153" t="n">
         <v>26413.98034179092</v>
@@ -4464,10 +4464,10 @@
         <v>209.0328363840779</v>
       </c>
       <c r="V35" s="149" t="n">
-        <v>282.5531265697411</v>
+        <v>282.553126569741</v>
       </c>
       <c r="W35" s="149" t="n">
-        <v>281.9232076557126</v>
+        <v>281.9232076557124</v>
       </c>
       <c r="X35" s="150" t="n">
         <v>302.8243163801429</v>
@@ -4482,22 +4482,22 @@
         <v>154.3604466595465</v>
       </c>
       <c r="AB35" s="149" t="n">
-        <v>137.6189286836234</v>
+        <v>137.6189286836233</v>
       </c>
       <c r="AC35" s="150" t="n">
         <v>133.0560575347765</v>
       </c>
       <c r="AD35" s="151" t="n">
-        <v>29030.43390703218</v>
+        <v>29030.43390703217</v>
       </c>
       <c r="AE35" s="152" t="n">
         <v>28819.57851442785</v>
       </c>
       <c r="AF35" s="152" t="n">
-        <v>29071.45646586571</v>
+        <v>29071.4564658657</v>
       </c>
       <c r="AG35" s="152" t="n">
-        <v>26536.01226448546</v>
+        <v>26536.01226448544</v>
       </c>
       <c r="AH35" s="153" t="n">
         <v>26413.98034179092</v>
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c r="C36" s="155" t="n">
-        <v>329.0274673884235</v>
+        <v>329.0274673884236</v>
       </c>
       <c r="D36" s="156" t="n">
         <v>431.7228679567916</v>
@@ -4519,25 +4519,25 @@
         <v>580.9695888307106</v>
       </c>
       <c r="F36" s="156" t="n">
-        <v>640.7480713681732</v>
+        <v>640.7480713681731</v>
       </c>
       <c r="G36" s="157" t="n">
-        <v>672.1270045287202</v>
+        <v>672.12700452872</v>
       </c>
       <c r="H36" s="155" t="n">
-        <v>286.1132968432141</v>
+        <v>286.1132968432142</v>
       </c>
       <c r="I36" s="156" t="n">
-        <v>294.6615670797992</v>
+        <v>294.6615670797991</v>
       </c>
       <c r="J36" s="156" t="n">
         <v>309.1839420522298</v>
       </c>
       <c r="K36" s="156" t="n">
-        <v>324.6366645912325</v>
+        <v>324.6366645912324</v>
       </c>
       <c r="L36" s="157" t="n">
-        <v>336.2939172269481</v>
+        <v>336.293917226948</v>
       </c>
       <c r="M36" s="158" t="n">
         <v>26390.48833790593</v>
@@ -4549,10 +4549,10 @@
         <v>30440.21472605048</v>
       </c>
       <c r="P36" s="159" t="n">
-        <v>33147.92366319875</v>
+        <v>33147.92366319874</v>
       </c>
       <c r="Q36" s="160" t="n">
-        <v>35753.21613392361</v>
+        <v>35753.2161339236</v>
       </c>
       <c r="S36" s="32" t="inlineStr">
         <is>
@@ -4569,10 +4569,10 @@
         <v>583.5909192006426</v>
       </c>
       <c r="W36" s="156" t="n">
-        <v>643.6391217970489</v>
+        <v>643.6391217970488</v>
       </c>
       <c r="X36" s="157" t="n">
-        <v>675.1596364655632</v>
+        <v>675.159636465563</v>
       </c>
       <c r="Y36" s="155" t="n">
         <v>287.2352036599424</v>
@@ -4584,10 +4584,10 @@
         <v>309.9247968355301</v>
       </c>
       <c r="AB36" s="156" t="n">
-        <v>325.3771398135657</v>
+        <v>325.3771398135656</v>
       </c>
       <c r="AC36" s="157" t="n">
-        <v>337.0514074746674</v>
+        <v>337.0514074746673</v>
       </c>
       <c r="AD36" s="158" t="n">
         <v>26390.48833790593</v>
@@ -4599,10 +4599,10 @@
         <v>30440.21472605048</v>
       </c>
       <c r="AG36" s="159" t="n">
-        <v>33147.92366319875</v>
+        <v>33147.92366319874</v>
       </c>
       <c r="AH36" s="160" t="n">
-        <v>35753.21613392361</v>
+        <v>35753.2161339236</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" thickTop="1">
@@ -4618,16 +4618,16 @@
         <v>289.0804473893925</v>
       </c>
       <c r="E37" s="162" t="n">
-        <v>394.9104662771339</v>
+        <v>394.9104662771338</v>
       </c>
       <c r="F37" s="162" t="n">
-        <v>421.3138169738658</v>
+        <v>421.3138169738656</v>
       </c>
       <c r="G37" s="163" t="n">
         <v>455.3354864226845</v>
       </c>
       <c r="H37" s="161" t="n">
-        <v>207.1301217521419</v>
+        <v>207.1301217521418</v>
       </c>
       <c r="I37" s="162" t="n">
         <v>206.9785795450014</v>
@@ -4636,7 +4636,7 @@
         <v>210.8840495803798</v>
       </c>
       <c r="K37" s="162" t="n">
-        <v>205.2874330935731</v>
+        <v>205.287433093573</v>
       </c>
       <c r="L37" s="163" t="n">
         <v>206.5739458472233</v>
@@ -4648,10 +4648,10 @@
         <v>56843.67223233398</v>
       </c>
       <c r="O37" s="165" t="n">
-        <v>59511.67119191619</v>
+        <v>59511.67119191618</v>
       </c>
       <c r="P37" s="165" t="n">
-        <v>59683.93592768422</v>
+        <v>59683.93592768419</v>
       </c>
       <c r="Q37" s="166" t="n">
         <v>62167.19647571453</v>
@@ -4668,10 +4668,10 @@
         <v>280.7209706479954</v>
       </c>
       <c r="V37" s="162" t="n">
-        <v>383.8257840778202</v>
+        <v>383.8257840778201</v>
       </c>
       <c r="W37" s="162" t="n">
-        <v>409.8446415327942</v>
+        <v>409.844641532794</v>
       </c>
       <c r="X37" s="163" t="n">
         <v>443.4792172878425</v>
@@ -4683,7 +4683,7 @@
         <v>202.6576817750087</v>
       </c>
       <c r="AA37" s="162" t="n">
-        <v>207.6812375414589</v>
+        <v>207.6812375414588</v>
       </c>
       <c r="AB37" s="162" t="n">
         <v>202.5259005282402</v>
@@ -4698,10 +4698,10 @@
         <v>56843.67223233398</v>
       </c>
       <c r="AF37" s="165" t="n">
-        <v>59511.67119191619</v>
+        <v>59511.67119191618</v>
       </c>
       <c r="AG37" s="165" t="n">
-        <v>59683.93592768422</v>
+        <v>59683.93592768419</v>
       </c>
       <c r="AH37" s="166" t="n">
         <v>62167.19647571453</v>
@@ -4714,7 +4714,7 @@
         </is>
       </c>
       <c r="C38" s="155" t="n">
-        <v>627.4244652073295</v>
+        <v>627.4244652073297</v>
       </c>
       <c r="D38" s="156" t="n">
         <v>780.5008674312877</v>
@@ -4729,7 +4729,7 @@
         <v>1249.733595312499</v>
       </c>
       <c r="H38" s="155" t="n">
-        <v>611.7216765137534</v>
+        <v>611.7216765137537</v>
       </c>
       <c r="I38" s="156" t="n">
         <v>692.6292998076676</v>
@@ -4744,7 +4744,7 @@
         <v>810.265685069118</v>
       </c>
       <c r="M38" s="158" t="n">
-        <v>61594.32945386381</v>
+        <v>61594.32945386384</v>
       </c>
       <c r="N38" s="159" t="n">
         <v>73745.15902253076</v>
@@ -4764,7 +4764,7 @@
         </is>
       </c>
       <c r="T38" s="155" t="n">
-        <v>751.7608347512588</v>
+        <v>751.7608347512592</v>
       </c>
       <c r="U38" s="156" t="n">
         <v>935.1723054508842</v>
@@ -4779,7 +4779,7 @@
         <v>1497.392631188461</v>
       </c>
       <c r="Y38" s="155" t="n">
-        <v>729.329007566609</v>
+        <v>729.3290075666092</v>
       </c>
       <c r="Z38" s="156" t="n">
         <v>811.7760462769139</v>
@@ -4794,7 +4794,7 @@
         <v>907.5892055866394</v>
       </c>
       <c r="AD38" s="158" t="n">
-        <v>61594.32945386381</v>
+        <v>61594.32945386384</v>
       </c>
       <c r="AE38" s="159" t="n">
         <v>73745.15902253076</v>
@@ -4816,7 +4816,7 @@
         </is>
       </c>
       <c r="C39" s="161" t="n">
-        <v>341.7327384980749</v>
+        <v>341.732738498075</v>
       </c>
       <c r="D39" s="162" t="n">
         <v>448.5730061708549</v>
@@ -4825,22 +4825,22 @@
         <v>614.8718299752737</v>
       </c>
       <c r="F39" s="162" t="n">
-        <v>700.8018094673246</v>
+        <v>700.8018094673243</v>
       </c>
       <c r="G39" s="163" t="n">
-        <v>754.7870959217456</v>
+        <v>754.7870959217457</v>
       </c>
       <c r="H39" s="161" t="n">
         <v>317.7553091152714</v>
       </c>
       <c r="I39" s="162" t="n">
-        <v>342.6567355261588</v>
+        <v>342.6567355261589</v>
       </c>
       <c r="J39" s="162" t="n">
         <v>370.2790686832155</v>
       </c>
       <c r="K39" s="162" t="n">
-        <v>384.45168471087</v>
+        <v>384.4516847108699</v>
       </c>
       <c r="L39" s="163" t="n">
         <v>386.1320915199492</v>
@@ -4875,13 +4875,13 @@
         <v>641.9640981383862</v>
       </c>
       <c r="W39" s="162" t="n">
-        <v>732.7561853083957</v>
+        <v>732.7561853083954</v>
       </c>
       <c r="X39" s="163" t="n">
         <v>790.9234692219261</v>
       </c>
       <c r="Y39" s="161" t="n">
-        <v>325.6628710559531</v>
+        <v>325.6628710559532</v>
       </c>
       <c r="Z39" s="162" t="n">
         <v>351.6736278043523</v>
@@ -4890,7 +4890,7 @@
         <v>379.9348705613184</v>
       </c>
       <c r="AB39" s="162" t="n">
-        <v>393.8743796705656</v>
+        <v>393.8743796705655</v>
       </c>
       <c r="AC39" s="163" t="n">
         <v>395.3733022150793</v>
@@ -5020,7 +5020,7 @@
         </is>
       </c>
       <c r="C41" s="179" t="n">
-        <v>338.6375012084546</v>
+        <v>338.6375012084547</v>
       </c>
       <c r="D41" s="180" t="n">
         <v>443.7133245253614</v>
@@ -5029,7 +5029,7 @@
         <v>606.5183649528163</v>
       </c>
       <c r="F41" s="180" t="n">
-        <v>690.5534757742371</v>
+        <v>690.553475774237</v>
       </c>
       <c r="G41" s="181" t="n">
         <v>743.2392508808379</v>
@@ -5044,7 +5044,7 @@
         <v>367.2332136988884</v>
       </c>
       <c r="K41" s="180" t="n">
-        <v>381.3469622224085</v>
+        <v>381.3469622224084</v>
       </c>
       <c r="L41" s="181" t="n">
         <v>383.0871335163905</v>
@@ -5079,13 +5079,13 @@
         <v>617.1170707532131</v>
       </c>
       <c r="W41" s="186" t="n">
-        <v>702.2444729165368</v>
+        <v>702.2444729165364</v>
       </c>
       <c r="X41" s="187" t="n">
         <v>756.4397059550862</v>
       </c>
       <c r="Y41" s="185" t="n">
-        <v>317.9092991042336</v>
+        <v>317.9092991042337</v>
       </c>
       <c r="Z41" s="186" t="n">
         <v>343.4172018201848</v>
@@ -5094,7 +5094,7 @@
         <v>371.0921269462629</v>
       </c>
       <c r="AB41" s="186" t="n">
-        <v>384.8854499506679</v>
+        <v>384.8854499506678</v>
       </c>
       <c r="AC41" s="187" t="n">
         <v>386.5641365947679</v>
@@ -6334,7 +6334,7 @@
         </is>
       </c>
       <c r="C57" s="148" t="n">
-        <v>0.1287624819691243</v>
+        <v>0.1287624819691242</v>
       </c>
       <c r="D57" s="149" t="n">
         <v>0.01961737841367162</v>
@@ -6349,7 +6349,7 @@
         <v>0</v>
       </c>
       <c r="H57" s="148" t="n">
-        <v>0.1204724249210899</v>
+        <v>0.1204724249210898</v>
       </c>
       <c r="I57" s="149" t="n">
         <v>0.01439361485810032</v>
@@ -6364,10 +6364,10 @@
         <v>0</v>
       </c>
       <c r="M57" s="151" t="n">
-        <v>21.12216940191699</v>
+        <v>21.12216940191698</v>
       </c>
       <c r="N57" s="152" t="n">
-        <v>2.584078410532202</v>
+        <v>2.584078410532201</v>
       </c>
       <c r="O57" s="152" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         </is>
       </c>
       <c r="T57" s="148" t="n">
-        <v>0.1230214795883353</v>
+        <v>0.1230214795883352</v>
       </c>
       <c r="U57" s="149" t="n">
-        <v>0.01874271822962257</v>
+        <v>0.01874271822962256</v>
       </c>
       <c r="V57" s="149" t="n">
         <v>0</v>
@@ -6402,7 +6402,7 @@
         <v>0.11543239849718</v>
       </c>
       <c r="Z57" s="149" t="n">
-        <v>0.01391709152328003</v>
+        <v>0.01391709152328002</v>
       </c>
       <c r="AA57" s="149" t="n">
         <v>0</v>
@@ -6414,10 +6414,10 @@
         <v>0</v>
       </c>
       <c r="AD57" s="151" t="n">
-        <v>21.12216940191699</v>
+        <v>21.12216940191698</v>
       </c>
       <c r="AE57" s="152" t="n">
-        <v>2.584078410532202</v>
+        <v>2.584078410532201</v>
       </c>
       <c r="AF57" s="152" t="n">
         <v>0</v>
@@ -6439,7 +6439,7 @@
         <v>1.983466879944259</v>
       </c>
       <c r="D58" s="156" t="n">
-        <v>0.3539236137796895</v>
+        <v>0.3539236137796894</v>
       </c>
       <c r="E58" s="156" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
         <v>1.724768611886845</v>
       </c>
       <c r="I58" s="156" t="n">
-        <v>0.2415616461468203</v>
+        <v>0.2415616461468202</v>
       </c>
       <c r="J58" s="156" t="n">
         <v>0</v>
@@ -6489,7 +6489,7 @@
         <v>1.992416267433915</v>
       </c>
       <c r="U58" s="156" t="n">
-        <v>0.3555205144355466</v>
+        <v>0.3555205144355465</v>
       </c>
       <c r="V58" s="156" t="n">
         <v>0</v>
@@ -6504,7 +6504,7 @@
         <v>1.731531770692481</v>
       </c>
       <c r="Z58" s="156" t="n">
-        <v>0.2423044824545736</v>
+        <v>0.2423044824545735</v>
       </c>
       <c r="AA58" s="156" t="n">
         <v>0</v>
@@ -6541,7 +6541,7 @@
         <v>0.7378225677252895</v>
       </c>
       <c r="D59" s="162" t="n">
-        <v>0.1299763365534195</v>
+        <v>0.1299763365534194</v>
       </c>
       <c r="E59" s="162" t="n">
         <v>0</v>
@@ -6556,7 +6556,7 @@
         <v>0.6735212170763188</v>
       </c>
       <c r="I59" s="162" t="n">
-        <v>0.0930616987666837</v>
+        <v>0.09306169876668367</v>
       </c>
       <c r="J59" s="162" t="n">
         <v>0</v>
@@ -6571,7 +6571,7 @@
         <v>180.2111961608827</v>
       </c>
       <c r="N59" s="165" t="n">
-        <v>25.55804911651459</v>
+        <v>25.55804911651458</v>
       </c>
       <c r="O59" s="165" t="n">
         <v>0</v>
@@ -6591,7 +6591,7 @@
         <v>0.7164251440057219</v>
       </c>
       <c r="U59" s="162" t="n">
-        <v>0.1262177490316327</v>
+        <v>0.1262177490316326</v>
       </c>
       <c r="V59" s="162" t="n">
         <v>0</v>
@@ -6606,7 +6606,7 @@
         <v>0.6556456752532971</v>
       </c>
       <c r="Z59" s="162" t="n">
-        <v>0.09111893692361447</v>
+        <v>0.09111893692361445</v>
       </c>
       <c r="AA59" s="162" t="n">
         <v>0</v>
@@ -6621,7 +6621,7 @@
         <v>180.2111961608827</v>
       </c>
       <c r="AE59" s="165" t="n">
-        <v>25.55804911651459</v>
+        <v>25.55804911651458</v>
       </c>
       <c r="AF59" s="165" t="n">
         <v>0</v>
@@ -6742,10 +6742,10 @@
         </is>
       </c>
       <c r="C61" s="161" t="n">
-        <v>0.5262909294131162</v>
+        <v>0.5262909294131163</v>
       </c>
       <c r="D61" s="162" t="n">
-        <v>0.08779197128797511</v>
+        <v>0.08779197128797508</v>
       </c>
       <c r="E61" s="162" t="n">
         <v>0</v>
@@ -6775,7 +6775,7 @@
         <v>180.2111961608827</v>
       </c>
       <c r="N61" s="165" t="n">
-        <v>25.55804911651459</v>
+        <v>25.55804911651458</v>
       </c>
       <c r="O61" s="165" t="n">
         <v>0</v>
@@ -6795,7 +6795,7 @@
         <v>0.5404028377663317</v>
       </c>
       <c r="U61" s="162" t="n">
-        <v>0.09084108234041571</v>
+        <v>0.09084108234041569</v>
       </c>
       <c r="V61" s="162" t="n">
         <v>0</v>
@@ -6810,7 +6810,7 @@
         <v>0.5015422749270683</v>
       </c>
       <c r="Z61" s="162" t="n">
-        <v>0.06882741629615188</v>
+        <v>0.06882741629615187</v>
       </c>
       <c r="AA61" s="162" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
         <v>180.2111961608827</v>
       </c>
       <c r="AE61" s="165" t="n">
-        <v>25.55804911651459</v>
+        <v>25.55804911651458</v>
       </c>
       <c r="AF61" s="165" t="n">
         <v>0</v>
@@ -6946,10 +6946,10 @@
         </is>
       </c>
       <c r="C63" s="179" t="n">
-        <v>0.5215240600839794</v>
+        <v>0.5215240600839796</v>
       </c>
       <c r="D63" s="180" t="n">
-        <v>0.08684086405320904</v>
+        <v>0.08684086405320902</v>
       </c>
       <c r="E63" s="180" t="n">
         <v>0</v>
@@ -6979,7 +6979,7 @@
         <v>180.2111961608827</v>
       </c>
       <c r="N63" s="183" t="n">
-        <v>25.55804911651459</v>
+        <v>25.55804911651458</v>
       </c>
       <c r="O63" s="183" t="n">
         <v>0</v>
@@ -6999,7 +6999,7 @@
         <v>0.5265652353520356</v>
       </c>
       <c r="U63" s="186" t="n">
-        <v>0.08804721049580097</v>
+        <v>0.08804721049580094</v>
       </c>
       <c r="V63" s="186" t="n">
         <v>0</v>
@@ -7014,7 +7014,7 @@
         <v>0.4896012633439333</v>
       </c>
       <c r="Z63" s="186" t="n">
-        <v>0.06721151898853003</v>
+        <v>0.06721151898853002</v>
       </c>
       <c r="AA63" s="186" t="n">
         <v>0</v>
@@ -7029,7 +7029,7 @@
         <v>180.2111961608827</v>
       </c>
       <c r="AE63" s="189" t="n">
-        <v>25.55804911651459</v>
+        <v>25.55804911651458</v>
       </c>
       <c r="AF63" s="189" t="n">
         <v>0</v>
@@ -7297,49 +7297,49 @@
         </is>
       </c>
       <c r="C68" s="148" t="n">
-        <v>0.786255339573271</v>
+        <v>0.7862553395732704</v>
       </c>
       <c r="D68" s="149" t="n">
-        <v>0.5386236514696779</v>
+        <v>0.5386236514696777</v>
       </c>
       <c r="E68" s="149" t="n">
-        <v>0.33384377463038</v>
+        <v>0.3338437746303798</v>
       </c>
       <c r="F68" s="149" t="n">
         <v>0.163206324157908</v>
       </c>
       <c r="G68" s="150" t="n">
-        <v>0.1916738922266969</v>
+        <v>0.1916738922266968</v>
       </c>
       <c r="H68" s="148" t="n">
-        <v>0.7356342151610602</v>
+        <v>0.7356342151610598</v>
       </c>
       <c r="I68" s="149" t="n">
-        <v>0.3951976267794893</v>
+        <v>0.3951976267794891</v>
       </c>
       <c r="J68" s="149" t="n">
         <v>0.1785994541569897</v>
       </c>
       <c r="K68" s="149" t="n">
-        <v>0.0778094686427515</v>
+        <v>0.07780946864275147</v>
       </c>
       <c r="L68" s="150" t="n">
-        <v>0.08207122180880012</v>
+        <v>0.0820712218088001</v>
       </c>
       <c r="M68" s="151" t="n">
         <v>128.9771540720274</v>
       </c>
       <c r="N68" s="152" t="n">
-        <v>70.94963046615952</v>
+        <v>70.94963046615949</v>
       </c>
       <c r="O68" s="152" t="n">
-        <v>32.81720286375497</v>
+        <v>32.81720286375496</v>
       </c>
       <c r="P68" s="152" t="n">
         <v>14.67686911281052</v>
       </c>
       <c r="Q68" s="153" t="n">
-        <v>15.97341126043841</v>
+        <v>15.9734112604384</v>
       </c>
       <c r="S68" s="21" t="inlineStr">
         <is>
@@ -7347,49 +7347,49 @@
         </is>
       </c>
       <c r="T68" s="148" t="n">
-        <v>0.7511993690190487</v>
+        <v>0.7511993690190483</v>
       </c>
       <c r="U68" s="149" t="n">
-        <v>0.5146085842066986</v>
+        <v>0.5146085842066984</v>
       </c>
       <c r="V68" s="149" t="n">
-        <v>0.3189590203474968</v>
+        <v>0.3189590203474966</v>
       </c>
       <c r="W68" s="149" t="n">
-        <v>0.155929609068065</v>
+        <v>0.1559296090680649</v>
       </c>
       <c r="X68" s="150" t="n">
         <v>0.183127922509583</v>
       </c>
       <c r="Y68" s="148" t="n">
-        <v>0.7048585759625264</v>
+        <v>0.704858575962526</v>
       </c>
       <c r="Z68" s="149" t="n">
-        <v>0.3821139856731658</v>
+        <v>0.3821139856731656</v>
       </c>
       <c r="AA68" s="149" t="n">
         <v>0.1742492020691856</v>
       </c>
       <c r="AB68" s="149" t="n">
-        <v>0.07611599601338633</v>
+        <v>0.0761159960133863</v>
       </c>
       <c r="AC68" s="150" t="n">
-        <v>0.08046341748550856</v>
+        <v>0.08046341748550852</v>
       </c>
       <c r="AD68" s="151" t="n">
         <v>128.9771540720274</v>
       </c>
       <c r="AE68" s="152" t="n">
-        <v>70.94963046615952</v>
+        <v>70.94963046615949</v>
       </c>
       <c r="AF68" s="152" t="n">
-        <v>32.81720286375497</v>
+        <v>32.81720286375496</v>
       </c>
       <c r="AG68" s="152" t="n">
         <v>14.67686911281052</v>
       </c>
       <c r="AH68" s="153" t="n">
-        <v>15.97341126043841</v>
+        <v>15.9734112604384</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" thickBot="1">
@@ -7414,19 +7414,19 @@
         <v>1.710346815181095</v>
       </c>
       <c r="H69" s="155" t="n">
-        <v>1.35261416558386</v>
+        <v>1.352614165583859</v>
       </c>
       <c r="I69" s="156" t="n">
         <v>0.7068325252656223</v>
       </c>
       <c r="J69" s="156" t="n">
-        <v>0.7730950101820778</v>
+        <v>0.7730950101820777</v>
       </c>
       <c r="K69" s="156" t="n">
-        <v>0.8116847518068827</v>
+        <v>0.8116847518068826</v>
       </c>
       <c r="L69" s="157" t="n">
-        <v>0.8557597394813615</v>
+        <v>0.8557597394813613</v>
       </c>
       <c r="M69" s="158" t="n">
         <v>124.7622838797603</v>
@@ -7435,13 +7435,13 @@
         <v>67.2240398611049</v>
       </c>
       <c r="O69" s="159" t="n">
-        <v>76.11384329139972</v>
+        <v>76.1138432913997</v>
       </c>
       <c r="P69" s="159" t="n">
-        <v>82.87931440324323</v>
+        <v>82.87931440324321</v>
       </c>
       <c r="Q69" s="160" t="n">
-        <v>90.98042324607212</v>
+        <v>90.98042324607211</v>
       </c>
       <c r="S69" s="32" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         <v>1.040287094456523</v>
       </c>
       <c r="V69" s="156" t="n">
-        <v>1.459232405884047</v>
+        <v>1.459232405884046</v>
       </c>
       <c r="W69" s="156" t="n">
         <v>1.609282369527977</v>
@@ -7470,13 +7470,13 @@
         <v>0.7090061354874583</v>
       </c>
       <c r="AA69" s="156" t="n">
-        <v>0.7749474709937142</v>
+        <v>0.7749474709937141</v>
       </c>
       <c r="AB69" s="156" t="n">
-        <v>0.8135361521957312</v>
+        <v>0.8135361521957311</v>
       </c>
       <c r="AC69" s="157" t="n">
-        <v>0.8576873082652193</v>
+        <v>0.8576873082652192</v>
       </c>
       <c r="AD69" s="158" t="n">
         <v>124.7622838797603</v>
@@ -7485,13 +7485,13 @@
         <v>67.2240398611049</v>
       </c>
       <c r="AF69" s="159" t="n">
-        <v>76.11384329139972</v>
+        <v>76.1138432913997</v>
       </c>
       <c r="AG69" s="159" t="n">
-        <v>82.87931440324323</v>
+        <v>82.87931440324321</v>
       </c>
       <c r="AH69" s="160" t="n">
-        <v>90.98042324607212</v>
+        <v>90.98042324607211</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" thickTop="1">
@@ -7501,37 +7501,37 @@
         </is>
       </c>
       <c r="C70" s="161" t="n">
-        <v>1.038862665755933</v>
+        <v>1.038862665755932</v>
       </c>
       <c r="D70" s="162" t="n">
         <v>0.7026869459168995</v>
       </c>
       <c r="E70" s="162" t="n">
-        <v>0.7228499782918467</v>
+        <v>0.7228499782918465</v>
       </c>
       <c r="F70" s="162" t="n">
-        <v>0.6886571303935504</v>
+        <v>0.6886571303935503</v>
       </c>
       <c r="G70" s="163" t="n">
-        <v>0.7833693494416748</v>
+        <v>0.7833693494416746</v>
       </c>
       <c r="H70" s="161" t="n">
-        <v>0.9483256241026226</v>
+        <v>0.9483256241026221</v>
       </c>
       <c r="I70" s="162" t="n">
         <v>0.5031165104528335</v>
       </c>
       <c r="J70" s="162" t="n">
-        <v>0.3860052940564485</v>
+        <v>0.3860052940564483</v>
       </c>
       <c r="K70" s="162" t="n">
-        <v>0.3355519066417121</v>
+        <v>0.335551906641712</v>
       </c>
       <c r="L70" s="163" t="n">
-        <v>0.3553944342034421</v>
+        <v>0.355394434203442</v>
       </c>
       <c r="M70" s="164" t="n">
-        <v>253.7394379517877</v>
+        <v>253.7394379517876</v>
       </c>
       <c r="N70" s="165" t="n">
         <v>138.1736703272644</v>
@@ -7540,7 +7540,7 @@
         <v>108.9310461551547</v>
       </c>
       <c r="P70" s="165" t="n">
-        <v>97.55618351605375</v>
+        <v>97.55618351605374</v>
       </c>
       <c r="Q70" s="166" t="n">
         <v>106.9538345065105</v>
@@ -7551,37 +7551,37 @@
         </is>
       </c>
       <c r="T70" s="161" t="n">
-        <v>1.008734846930668</v>
+        <v>1.008734846930667</v>
       </c>
       <c r="U70" s="162" t="n">
         <v>0.6823670134070287</v>
       </c>
       <c r="V70" s="162" t="n">
-        <v>0.702560411487803</v>
+        <v>0.7025604114878028</v>
       </c>
       <c r="W70" s="162" t="n">
         <v>0.66991022694766</v>
       </c>
       <c r="X70" s="163" t="n">
-        <v>0.762971558986255</v>
+        <v>0.7629715589862548</v>
       </c>
       <c r="Y70" s="161" t="n">
-        <v>0.9231566555152992</v>
+        <v>0.9231566555152989</v>
       </c>
       <c r="Z70" s="162" t="n">
         <v>0.492613418718215</v>
       </c>
       <c r="AA70" s="162" t="n">
-        <v>0.3801428193678639</v>
+        <v>0.3801428193678638</v>
       </c>
       <c r="AB70" s="162" t="n">
-        <v>0.3310380525611838</v>
+        <v>0.3310380525611837</v>
       </c>
       <c r="AC70" s="163" t="n">
-        <v>0.3511355713863034</v>
+        <v>0.3511355713863033</v>
       </c>
       <c r="AD70" s="164" t="n">
-        <v>253.7394379517877</v>
+        <v>253.7394379517876</v>
       </c>
       <c r="AE70" s="165" t="n">
         <v>138.1736703272644</v>
@@ -7590,7 +7590,7 @@
         <v>108.9310461551547</v>
       </c>
       <c r="AG70" s="165" t="n">
-        <v>97.55618351605375</v>
+        <v>97.55618351605374</v>
       </c>
       <c r="AH70" s="166" t="n">
         <v>106.9538345065105</v>
@@ -7615,7 +7615,7 @@
         <v>2.318162421270879</v>
       </c>
       <c r="G71" s="157" t="n">
-        <v>4.188620606328712</v>
+        <v>4.188620606328711</v>
       </c>
       <c r="H71" s="155" t="n">
         <v>0.5473983630888758</v>
@@ -7665,7 +7665,7 @@
         <v>2.777551424182554</v>
       </c>
       <c r="X71" s="157" t="n">
-        <v>5.018677303935664</v>
+        <v>5.018677303935663</v>
       </c>
       <c r="Y71" s="155" t="n">
         <v>0.6526391334870737</v>
@@ -7705,13 +7705,13 @@
         </is>
       </c>
       <c r="C72" s="161" t="n">
-        <v>0.9019898033153386</v>
+        <v>0.9019898033153384</v>
       </c>
       <c r="D72" s="162" t="n">
         <v>0.7338483740707017</v>
       </c>
       <c r="E72" s="162" t="n">
-        <v>0.9233683693765359</v>
+        <v>0.9233683693765358</v>
       </c>
       <c r="F72" s="162" t="n">
         <v>1.291935715845966</v>
@@ -7720,22 +7720,22 @@
         <v>2.066992709331823</v>
       </c>
       <c r="H72" s="161" t="n">
-        <v>0.8387023439163493</v>
+        <v>0.838702343916349</v>
       </c>
       <c r="I72" s="162" t="n">
-        <v>0.5605733844235588</v>
+        <v>0.5605733844235589</v>
       </c>
       <c r="J72" s="162" t="n">
         <v>0.5560573166574118</v>
       </c>
       <c r="K72" s="162" t="n">
-        <v>0.7087408391149194</v>
+        <v>0.7087408391149193</v>
       </c>
       <c r="L72" s="163" t="n">
-        <v>1.057426951683779</v>
+        <v>1.057426951683778</v>
       </c>
       <c r="M72" s="164" t="n">
-        <v>308.8570452119318</v>
+        <v>308.8570452119317</v>
       </c>
       <c r="N72" s="165" t="n">
         <v>213.638360244251</v>
@@ -7747,7 +7747,7 @@
         <v>290.606364099352</v>
       </c>
       <c r="Q72" s="166" t="n">
-        <v>452.9483415717776</v>
+        <v>452.9483415717775</v>
       </c>
       <c r="S72" s="42" t="inlineStr">
         <is>
@@ -7755,37 +7755,37 @@
         </is>
       </c>
       <c r="T72" s="161" t="n">
-        <v>0.9261756608487665</v>
+        <v>0.9261756608487661</v>
       </c>
       <c r="U72" s="162" t="n">
         <v>0.7593357296382719</v>
       </c>
       <c r="V72" s="162" t="n">
-        <v>0.9640535044842722</v>
+        <v>0.964053504484272</v>
       </c>
       <c r="W72" s="162" t="n">
-        <v>1.350843953337568</v>
+        <v>1.350843953337567</v>
       </c>
       <c r="X72" s="163" t="n">
         <v>2.165952562456962</v>
       </c>
       <c r="Y72" s="161" t="n">
-        <v>0.8595740352589089</v>
+        <v>0.8595740352589085</v>
       </c>
       <c r="Z72" s="162" t="n">
         <v>0.5753246771819167</v>
       </c>
       <c r="AA72" s="162" t="n">
-        <v>0.5705576752696535</v>
+        <v>0.5705576752696534</v>
       </c>
       <c r="AB72" s="162" t="n">
-        <v>0.7261116791919529</v>
+        <v>0.7261116791919526</v>
       </c>
       <c r="AC72" s="163" t="n">
-        <v>1.082734108146101</v>
+        <v>1.0827341081461</v>
       </c>
       <c r="AD72" s="164" t="n">
-        <v>308.8570452119318</v>
+        <v>308.8570452119317</v>
       </c>
       <c r="AE72" s="165" t="n">
         <v>213.638360244251</v>
@@ -7797,7 +7797,7 @@
         <v>290.606364099352</v>
       </c>
       <c r="AH72" s="166" t="n">
-        <v>452.9483415717776</v>
+        <v>452.9483415717775</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" thickBot="1">
@@ -7909,13 +7909,13 @@
         </is>
       </c>
       <c r="C74" s="179" t="n">
-        <v>0.8938200491198547</v>
+        <v>0.8938200491198545</v>
       </c>
       <c r="D74" s="180" t="n">
         <v>0.7258981197642973</v>
       </c>
       <c r="E74" s="180" t="n">
-        <v>0.9108237625163703</v>
+        <v>0.9108237625163701</v>
       </c>
       <c r="F74" s="180" t="n">
         <v>1.273042801833556</v>
@@ -7924,22 +7924,22 @@
         <v>2.035368809510244</v>
       </c>
       <c r="H74" s="179" t="n">
-        <v>0.8316343277471338</v>
+        <v>0.8316343277471334</v>
       </c>
       <c r="I74" s="180" t="n">
-        <v>0.5559223917645368</v>
+        <v>0.5559223917645369</v>
       </c>
       <c r="J74" s="180" t="n">
-        <v>0.5514832802271714</v>
+        <v>0.5514832802271713</v>
       </c>
       <c r="K74" s="180" t="n">
-        <v>0.703017249625785</v>
+        <v>0.7030172496257849</v>
       </c>
       <c r="L74" s="181" t="n">
         <v>1.049088300920425</v>
       </c>
       <c r="M74" s="182" t="n">
-        <v>308.8570452119318</v>
+        <v>308.8570452119317</v>
       </c>
       <c r="N74" s="183" t="n">
         <v>213.638360244251</v>
@@ -7951,7 +7951,7 @@
         <v>290.606364099352</v>
       </c>
       <c r="Q74" s="184" t="n">
-        <v>452.9483415717776</v>
+        <v>452.9483415717775</v>
       </c>
       <c r="S74" s="51" t="inlineStr">
         <is>
@@ -7959,37 +7959,37 @@
         </is>
       </c>
       <c r="T74" s="185" t="n">
-        <v>0.9024599257249536</v>
+        <v>0.9024599257249533</v>
       </c>
       <c r="U74" s="186" t="n">
         <v>0.735981904904036</v>
       </c>
       <c r="V74" s="186" t="n">
-        <v>0.926740103476091</v>
+        <v>0.9267401034760909</v>
       </c>
       <c r="W74" s="186" t="n">
-        <v>1.294595281518891</v>
+        <v>1.29459528151889</v>
       </c>
       <c r="X74" s="187" t="n">
         <v>2.071518399965302</v>
       </c>
       <c r="Y74" s="185" t="n">
-        <v>0.8391087942917715</v>
+        <v>0.8391087942917712</v>
       </c>
       <c r="Z74" s="186" t="n">
         <v>0.561817478351926</v>
       </c>
       <c r="AA74" s="186" t="n">
-        <v>0.5572783065384872</v>
+        <v>0.5572783065384871</v>
       </c>
       <c r="AB74" s="186" t="n">
-        <v>0.7095404900262282</v>
+        <v>0.7095404900262281</v>
       </c>
       <c r="AC74" s="187" t="n">
         <v>1.058610111841892</v>
       </c>
       <c r="AD74" s="188" t="n">
-        <v>308.8570452119318</v>
+        <v>308.8570452119317</v>
       </c>
       <c r="AE74" s="189" t="n">
         <v>213.638360244251</v>
@@ -8001,7 +8001,7 @@
         <v>290.606364099352</v>
       </c>
       <c r="AH74" s="190" t="n">
-        <v>452.9483415717776</v>
+        <v>452.9483415717775</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" thickBot="1"/>
@@ -8260,46 +8260,46 @@
         </is>
       </c>
       <c r="C79" s="148" t="n">
-        <v>177.8869306673333</v>
+        <v>177.8869306673332</v>
       </c>
       <c r="D79" s="149" t="n">
-        <v>219.3459431118849</v>
+        <v>219.3459431118848</v>
       </c>
       <c r="E79" s="149" t="n">
-        <v>296.0727829176261</v>
+        <v>296.0727829176259</v>
       </c>
       <c r="F79" s="149" t="n">
-        <v>295.242830337137</v>
+        <v>295.2428303371369</v>
       </c>
       <c r="G79" s="150" t="n">
         <v>317.147791703443</v>
       </c>
       <c r="H79" s="148" t="n">
-        <v>166.4341163010682</v>
+        <v>166.4341163010681</v>
       </c>
       <c r="I79" s="149" t="n">
         <v>160.9379683290898</v>
       </c>
       <c r="J79" s="149" t="n">
-        <v>158.3927616394048</v>
+        <v>158.3927616394047</v>
       </c>
       <c r="K79" s="149" t="n">
-        <v>140.7585635400241</v>
+        <v>140.758563540024</v>
       </c>
       <c r="L79" s="150" t="n">
         <v>135.796828961347</v>
       </c>
       <c r="M79" s="151" t="n">
-        <v>29180.53323050612</v>
+        <v>29180.53323050611</v>
       </c>
       <c r="N79" s="152" t="n">
         <v>28893.11222330454</v>
       </c>
       <c r="O79" s="152" t="n">
-        <v>29104.27366872947</v>
+        <v>29104.27366872946</v>
       </c>
       <c r="P79" s="152" t="n">
-        <v>26550.68913359827</v>
+        <v>26550.68913359825</v>
       </c>
       <c r="Q79" s="153" t="n">
         <v>26429.95375305136</v>
@@ -8316,16 +8316,16 @@
         <v>209.5661876865142</v>
       </c>
       <c r="V79" s="149" t="n">
-        <v>282.8720855900886</v>
+        <v>282.8720855900885</v>
       </c>
       <c r="W79" s="149" t="n">
-        <v>282.0791372647806</v>
+        <v>282.0791372647804</v>
       </c>
       <c r="X79" s="150" t="n">
         <v>303.0074443026525</v>
       </c>
       <c r="Y79" s="148" t="n">
-        <v>159.4712586633399</v>
+        <v>159.4712586633398</v>
       </c>
       <c r="Z79" s="149" t="n">
         <v>155.6098629071067</v>
@@ -8340,16 +8340,16 @@
         <v>133.136520952262</v>
       </c>
       <c r="AD79" s="151" t="n">
-        <v>29180.53323050612</v>
+        <v>29180.53323050611</v>
       </c>
       <c r="AE79" s="152" t="n">
         <v>28893.11222330454</v>
       </c>
       <c r="AF79" s="152" t="n">
-        <v>29104.27366872947</v>
+        <v>29104.27366872946</v>
       </c>
       <c r="AG79" s="152" t="n">
-        <v>26550.68913359827</v>
+        <v>26550.68913359825</v>
       </c>
       <c r="AH79" s="153" t="n">
         <v>26429.95375305136</v>
@@ -8365,16 +8365,16 @@
         <v>332.566427208284</v>
       </c>
       <c r="D80" s="156" t="n">
-        <v>433.1124059806792</v>
+        <v>433.1124059806791</v>
       </c>
       <c r="E80" s="156" t="n">
         <v>582.4222667647952</v>
       </c>
       <c r="F80" s="156" t="n">
-        <v>642.3501252826135</v>
+        <v>642.3501252826134</v>
       </c>
       <c r="G80" s="157" t="n">
-        <v>673.8373513439013</v>
+        <v>673.8373513439011</v>
       </c>
       <c r="H80" s="155" t="n">
         <v>289.1906796206849</v>
@@ -8386,25 +8386,25 @@
         <v>309.9570370624119</v>
       </c>
       <c r="K80" s="156" t="n">
-        <v>325.4483493430394</v>
+        <v>325.4483493430393</v>
       </c>
       <c r="L80" s="157" t="n">
-        <v>337.1496769664295</v>
+        <v>337.1496769664294</v>
       </c>
       <c r="M80" s="158" t="n">
-        <v>26674.33964854465</v>
+        <v>26674.33964854466</v>
       </c>
       <c r="N80" s="159" t="n">
-        <v>28114.29172847322</v>
+        <v>28114.29172847321</v>
       </c>
       <c r="O80" s="159" t="n">
         <v>30516.32856934188</v>
       </c>
       <c r="P80" s="159" t="n">
-        <v>33230.802977602</v>
+        <v>33230.80297760199</v>
       </c>
       <c r="Q80" s="160" t="n">
-        <v>35844.19655716969</v>
+        <v>35844.19655716968</v>
       </c>
       <c r="S80" s="32" t="inlineStr">
         <is>
@@ -8412,7 +8412,7 @@
         </is>
       </c>
       <c r="T80" s="155" t="n">
-        <v>334.0669644006272</v>
+        <v>334.0669644006273</v>
       </c>
       <c r="U80" s="156" t="n">
         <v>435.06660586518</v>
@@ -8421,40 +8421,40 @@
         <v>585.0501516065267</v>
       </c>
       <c r="W80" s="156" t="n">
-        <v>645.248404166577</v>
+        <v>645.2484041665768</v>
       </c>
       <c r="X80" s="157" t="n">
-        <v>676.8777003525772</v>
+        <v>676.8777003525771</v>
       </c>
       <c r="Y80" s="155" t="n">
-        <v>290.3246534638457</v>
+        <v>290.3246534638458</v>
       </c>
       <c r="Z80" s="156" t="n">
-        <v>296.5190037902639</v>
+        <v>296.5190037902638</v>
       </c>
       <c r="AA80" s="156" t="n">
         <v>310.6997443065238</v>
       </c>
       <c r="AB80" s="156" t="n">
-        <v>326.1906759657614</v>
+        <v>326.1906759657613</v>
       </c>
       <c r="AC80" s="157" t="n">
-        <v>337.9090947829326</v>
+        <v>337.9090947829325</v>
       </c>
       <c r="AD80" s="158" t="n">
-        <v>26674.33964854465</v>
+        <v>26674.33964854466</v>
       </c>
       <c r="AE80" s="159" t="n">
-        <v>28114.29172847322</v>
+        <v>28114.29172847321</v>
       </c>
       <c r="AF80" s="159" t="n">
         <v>30516.32856934188</v>
       </c>
       <c r="AG80" s="159" t="n">
-        <v>33230.802977602</v>
+        <v>33230.80297760199</v>
       </c>
       <c r="AH80" s="160" t="n">
-        <v>35844.19655716969</v>
+        <v>35844.19655716968</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" thickTop="1">
@@ -8473,7 +8473,7 @@
         <v>395.6333162554257</v>
       </c>
       <c r="F81" s="162" t="n">
-        <v>422.0024741042593</v>
+        <v>422.0024741042592</v>
       </c>
       <c r="G81" s="163" t="n">
         <v>456.1188557721262</v>
@@ -8488,10 +8488,10 @@
         <v>211.2700548744362</v>
       </c>
       <c r="K81" s="162" t="n">
-        <v>205.6229850002148</v>
+        <v>205.6229850002147</v>
       </c>
       <c r="L81" s="163" t="n">
-        <v>206.9293402814268</v>
+        <v>206.9293402814267</v>
       </c>
       <c r="M81" s="164" t="n">
         <v>55854.87287905077</v>
@@ -8500,13 +8500,13 @@
         <v>57007.40395177776</v>
       </c>
       <c r="O81" s="165" t="n">
-        <v>59620.60223807134</v>
+        <v>59620.60223807133</v>
       </c>
       <c r="P81" s="165" t="n">
-        <v>59781.49211120026</v>
+        <v>59781.49211120024</v>
       </c>
       <c r="Q81" s="166" t="n">
-        <v>62274.15031022105</v>
+        <v>62274.15031022104</v>
       </c>
       <c r="S81" s="42" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         <v>384.5283444893079</v>
       </c>
       <c r="W81" s="162" t="n">
-        <v>410.5145517597418</v>
+        <v>410.5145517597417</v>
       </c>
       <c r="X81" s="163" t="n">
         <v>444.2421888468288</v>
@@ -8538,7 +8538,7 @@
         <v>208.0613803608267</v>
       </c>
       <c r="AB81" s="162" t="n">
-        <v>202.8569385808014</v>
+        <v>202.8569385808013</v>
       </c>
       <c r="AC81" s="163" t="n">
         <v>204.4496062499277</v>
@@ -8550,13 +8550,13 @@
         <v>57007.40395177776</v>
       </c>
       <c r="AF81" s="165" t="n">
-        <v>59620.60223807134</v>
+        <v>59620.60223807133</v>
       </c>
       <c r="AG81" s="165" t="n">
-        <v>59781.49211120026</v>
+        <v>59781.49211120024</v>
       </c>
       <c r="AH81" s="166" t="n">
-        <v>62274.15031022105</v>
+        <v>62274.15031022104</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" thickBot="1">
@@ -8566,7 +8566,7 @@
         </is>
       </c>
       <c r="C82" s="155" t="n">
-        <v>627.9859151908804</v>
+        <v>627.9859151908806</v>
       </c>
       <c r="D82" s="156" t="n">
         <v>781.2995673964291</v>
@@ -8581,7 +8581,7 @@
         <v>1253.922215918828</v>
       </c>
       <c r="H82" s="155" t="n">
-        <v>612.2690748768423</v>
+        <v>612.2690748768425</v>
       </c>
       <c r="I82" s="156" t="n">
         <v>693.3380792859441</v>
@@ -8596,7 +8596,7 @@
         <v>812.9813802843313</v>
       </c>
       <c r="M82" s="158" t="n">
-        <v>61649.44706112396</v>
+        <v>61649.44706112398</v>
       </c>
       <c r="N82" s="159" t="n">
         <v>73820.62371244775</v>
@@ -8616,7 +8616,7 @@
         </is>
       </c>
       <c r="T82" s="155" t="n">
-        <v>752.4335469767311</v>
+        <v>752.4335469767313</v>
       </c>
       <c r="U82" s="156" t="n">
         <v>936.1292833594714</v>
@@ -8631,7 +8631,7 @@
         <v>1502.411308492397</v>
       </c>
       <c r="Y82" s="155" t="n">
-        <v>729.981646700096</v>
+        <v>729.9816467000963</v>
       </c>
       <c r="Z82" s="156" t="n">
         <v>812.6067506706166</v>
@@ -8646,7 +8646,7 @@
         <v>910.6310913636246</v>
       </c>
       <c r="AD82" s="158" t="n">
-        <v>61649.44706112396</v>
+        <v>61649.44706112398</v>
       </c>
       <c r="AE82" s="159" t="n">
         <v>73820.62371244775</v>
@@ -8668,37 +8668,37 @@
         </is>
       </c>
       <c r="C83" s="161" t="n">
-        <v>343.1610192308033</v>
+        <v>343.1610192308034</v>
       </c>
       <c r="D83" s="162" t="n">
         <v>449.3946465162136</v>
       </c>
       <c r="E83" s="162" t="n">
-        <v>615.7951983446503</v>
+        <v>615.7951983446502</v>
       </c>
       <c r="F83" s="162" t="n">
         <v>702.0937451831704</v>
       </c>
       <c r="G83" s="163" t="n">
-        <v>756.8540886310774</v>
+        <v>756.8540886310775</v>
       </c>
       <c r="H83" s="161" t="n">
-        <v>319.0833755678043</v>
+        <v>319.0833755678044</v>
       </c>
       <c r="I83" s="162" t="n">
         <v>343.2843715957487</v>
       </c>
       <c r="J83" s="162" t="n">
-        <v>370.835125999873</v>
+        <v>370.8351259998729</v>
       </c>
       <c r="K83" s="162" t="n">
-        <v>385.1604255499849</v>
+        <v>385.1604255499848</v>
       </c>
       <c r="L83" s="163" t="n">
         <v>387.1895184716329</v>
       </c>
       <c r="M83" s="164" t="n">
-        <v>117504.3199401747</v>
+        <v>117504.3199401748</v>
       </c>
       <c r="N83" s="165" t="n">
         <v>130828.0276642255</v>
@@ -8707,7 +8707,7 @@
         <v>146342.9955547558</v>
       </c>
       <c r="P83" s="165" t="n">
-        <v>157928.0671956471</v>
+        <v>157928.067195647</v>
       </c>
       <c r="Q83" s="166" t="n">
         <v>165852.4496528507</v>
@@ -8718,28 +8718,28 @@
         </is>
       </c>
       <c r="T83" s="161" t="n">
-        <v>352.3625018768776</v>
+        <v>352.3625018768777</v>
       </c>
       <c r="U83" s="162" t="n">
-        <v>465.0026134350281</v>
+        <v>465.002613435028</v>
       </c>
       <c r="V83" s="162" t="n">
-        <v>642.9281516428706</v>
+        <v>642.9281516428705</v>
       </c>
       <c r="W83" s="162" t="n">
-        <v>734.1070292617333</v>
+        <v>734.107029261733</v>
       </c>
       <c r="X83" s="163" t="n">
         <v>793.0894217843829</v>
       </c>
       <c r="Y83" s="161" t="n">
-        <v>327.0239873661391</v>
+        <v>327.0239873661392</v>
       </c>
       <c r="Z83" s="162" t="n">
-        <v>352.3177798978304</v>
+        <v>352.3177798978303</v>
       </c>
       <c r="AA83" s="162" t="n">
-        <v>380.5054282365881</v>
+        <v>380.505428236588</v>
       </c>
       <c r="AB83" s="162" t="n">
         <v>394.6004913497575</v>
@@ -8748,7 +8748,7 @@
         <v>396.4560363232254</v>
       </c>
       <c r="AD83" s="164" t="n">
-        <v>117504.3199401747</v>
+        <v>117504.3199401748</v>
       </c>
       <c r="AE83" s="165" t="n">
         <v>130828.0276642255</v>
@@ -8757,7 +8757,7 @@
         <v>146342.9955547558</v>
       </c>
       <c r="AG83" s="165" t="n">
-        <v>157928.0671956471</v>
+        <v>157928.067195647</v>
       </c>
       <c r="AH83" s="166" t="n">
         <v>165852.4496528507</v>
@@ -8872,13 +8872,13 @@
         </is>
       </c>
       <c r="C85" s="179" t="n">
-        <v>340.0528453176584</v>
+        <v>340.0528453176586</v>
       </c>
       <c r="D85" s="180" t="n">
-        <v>444.526063509179</v>
+        <v>444.5260635091789</v>
       </c>
       <c r="E85" s="180" t="n">
-        <v>607.4291887153329</v>
+        <v>607.4291887153327</v>
       </c>
       <c r="F85" s="180" t="n">
         <v>691.8265185760706</v>
@@ -8887,22 +8887,22 @@
         <v>745.274619690348</v>
       </c>
       <c r="H85" s="179" t="n">
-        <v>316.3943566635409</v>
+        <v>316.394356663541</v>
       </c>
       <c r="I85" s="180" t="n">
         <v>340.4361930403387</v>
       </c>
       <c r="J85" s="180" t="n">
-        <v>367.7846969791157</v>
+        <v>367.7846969791156</v>
       </c>
       <c r="K85" s="180" t="n">
-        <v>382.0499794720343</v>
+        <v>382.0499794720342</v>
       </c>
       <c r="L85" s="181" t="n">
         <v>384.1362218173109</v>
       </c>
       <c r="M85" s="182" t="n">
-        <v>117504.3199401747</v>
+        <v>117504.3199401748</v>
       </c>
       <c r="N85" s="183" t="n">
         <v>130828.0276642255</v>
@@ -8911,7 +8911,7 @@
         <v>146342.9955547558</v>
       </c>
       <c r="P85" s="183" t="n">
-        <v>157928.0671956471</v>
+        <v>157928.067195647</v>
       </c>
       <c r="Q85" s="184" t="n">
         <v>165852.4496528507</v>
@@ -8925,25 +8925,25 @@
         <v>343.3398767795846</v>
       </c>
       <c r="U85" s="186" t="n">
-        <v>450.7011798118579</v>
+        <v>450.7011798118578</v>
       </c>
       <c r="V85" s="186" t="n">
-        <v>618.0438108566892</v>
+        <v>618.0438108566891</v>
       </c>
       <c r="W85" s="186" t="n">
-        <v>703.5390681980556</v>
+        <v>703.5390681980554</v>
       </c>
       <c r="X85" s="187" t="n">
         <v>758.5112243550515</v>
       </c>
       <c r="Y85" s="185" t="n">
-        <v>319.2380091618693</v>
+        <v>319.2380091618694</v>
       </c>
       <c r="Z85" s="186" t="n">
         <v>344.0462308175253</v>
       </c>
       <c r="AA85" s="186" t="n">
-        <v>371.6494052528014</v>
+        <v>371.6494052528013</v>
       </c>
       <c r="AB85" s="186" t="n">
         <v>385.5949904406941</v>
@@ -8952,7 +8952,7 @@
         <v>387.6227467066097</v>
       </c>
       <c r="AD85" s="188" t="n">
-        <v>117504.3199401747</v>
+        <v>117504.3199401748</v>
       </c>
       <c r="AE85" s="189" t="n">
         <v>130828.0276642255</v>
@@ -8961,7 +8961,7 @@
         <v>146342.9955547558</v>
       </c>
       <c r="AG85" s="189" t="n">
-        <v>157928.0671956471</v>
+        <v>157928.067195647</v>
       </c>
       <c r="AH85" s="190" t="n">
         <v>165852.4496528507</v>
@@ -9789,7 +9789,7 @@
         <v>368.2558507821897</v>
       </c>
       <c r="N94" s="86" t="n">
-        <v>381.1068562663507</v>
+        <v>381.1068562663506</v>
       </c>
       <c r="O94" s="86" t="n">
         <v>394.6308892939284</v>
@@ -9988,7 +9988,7 @@
         </is>
       </c>
       <c r="C96" s="132" t="n">
-        <v>345.5472334907498</v>
+        <v>345.5472334907497</v>
       </c>
       <c r="D96" s="133" t="n">
         <v>294.3090144848707</v>
@@ -10021,7 +10021,7 @@
         <v>371.3856377821897</v>
       </c>
       <c r="N96" s="133" t="n">
-        <v>384.2952962663507</v>
+        <v>384.2952962663506</v>
       </c>
       <c r="O96" s="133" t="n">
         <v>397.9039822939284</v>
